--- a/3_sekiguchi/関口実験.xlsx
+++ b/3_sekiguchi/関口実験.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/takumi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/takumi/Documents/4e_zikken/3_sekiguchi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABB1CFF-7555-584A-A9B5-103114AFB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267CDFF3-03A7-2C4C-82DD-849ABB31B9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{89831BD7-977B-D94C-A7FA-04153F44CAF8}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="6" xr2:uid="{89831BD7-977B-D94C-A7FA-04153F44CAF8}"/>
   </bookViews>
   <sheets>
     <sheet name="実験2.1 無負荷試験" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="88">
   <si>
     <t>W_i</t>
     <phoneticPr fontId="1"/>
@@ -461,6 +461,23 @@
   <si>
     <t>NewFile5.bmp</t>
   </si>
+  <si>
+    <t>電圧計</t>
+    <rPh sb="0" eb="2">
+      <t>デンアｔウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種別</t>
+    <rPh sb="0" eb="2">
+      <t>シュベｔウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -470,7 +487,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
     <numFmt numFmtId="178" formatCode="0.0000"/>
-    <numFmt numFmtId="183" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="179" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -512,7 +529,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -883,13 +900,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -998,7 +1026,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1007,97 +1035,103 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,37 +1186,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -1314,101 +1318,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-3339-4446-8BE0-C516341EBDC3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'実験2.1 無負荷試験'!$E$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>W_0 [W]</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>''実験2.1 無負荷試験'!$B$3:$B$13</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'実験2.1 無負荷試験'!$E$3:$E$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.42000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.1599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.4400000000000004</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.98</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10.740000000000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>15.100000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-3339-4446-8BE0-C516341EBDC3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1713,6 +1622,62 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>V_0 [V]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1775,6 +1740,70 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>鉄損</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>W_i [W]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1823,6 +1852,78 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>無負荷力率</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t> p.f.</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>　電流</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>I_0 [A]</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -3778,10 +3879,10 @@
       <xdr:rowOff>39650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>404707</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>287130</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>90507</xdr:rowOff>
+      <xdr:rowOff>143565</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4822,10 +4923,10 @@
       <c r="F2" s="39">
         <v>43.4</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="6" t="s">
         <v>78</v>
       </c>
       <c r="J2" t="s">
@@ -4836,10 +4937,10 @@
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
       <c r="D3" s="40"/>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="41">
         <v>42.6</v>
       </c>
       <c r="I3" t="s">
@@ -4852,17 +4953,17 @@
     <row r="4" spans="2:10">
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44" t="s">
+      <c r="D4" s="42"/>
+      <c r="E4" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="44">
         <v>42.7</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="6" t="s">
         <v>78</v>
       </c>
       <c r="J4" t="s">
@@ -4892,10 +4993,10 @@
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="41">
         <v>80</v>
       </c>
       <c r="H6" t="s">
@@ -4907,18 +5008,18 @@
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="40"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="44" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="44">
         <v>79.3</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" s="40"/>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="48" t="s">
         <v>70</v>
       </c>
       <c r="D8" s="37" t="s">
@@ -4935,21 +5036,21 @@
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40"/>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <v>47.1</v>
       </c>
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="42"/>
+      <c r="E10" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <v>47.3</v>
       </c>
     </row>
@@ -4959,10 +5060,10 @@
       <c r="D11" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="41">
         <v>88.8</v>
       </c>
     </row>
@@ -4970,29 +5071,29 @@
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="41">
         <v>88.6</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="44">
         <v>87.3</v>
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="45" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -5006,30 +5107,30 @@
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
       <c r="D17" s="40"/>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="41">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44" t="s">
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="44">
         <v>44.9</v>
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="37" t="s">
         <v>55</v>
       </c>
@@ -5041,30 +5142,30 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <v>84.9</v>
       </c>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="44" t="s">
+      <c r="B21" s="46"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="44">
         <v>83.2</v>
       </c>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="47"/>
-      <c r="C22" s="49" t="s">
+      <c r="B22" s="46"/>
+      <c r="C22" s="48" t="s">
         <v>70</v>
       </c>
       <c r="D22" s="37" t="s">
@@ -5078,30 +5179,30 @@
       </c>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="41">
         <v>49.5</v>
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="44" t="s">
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="45">
+      <c r="F24" s="44">
         <v>49.1</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="37" t="s">
         <v>55</v>
       </c>
@@ -5113,29 +5214,43 @@
       </c>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="41" t="s">
+      <c r="E26" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="42">
+      <c r="F26" s="41">
         <v>49.5</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="44" t="s">
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="44">
         <v>47.9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C7A2C493-A311-4544-9E0F-FF3C2903DE1A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F27">
     <cfRule type="dataBar" priority="2">
       <dataBar>
@@ -5150,25 +5265,22 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C7A2C493-A311-4544-9E0F-FF3C2903DE1A}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C7A2C493-A311-4544-9E0F-FF3C2903DE1A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F1:F1048576</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{4445FABB-C76A-6544-83EE-BDEA1D0DB3CA}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
@@ -5179,17 +5291,6 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>F2:F27</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C7A2C493-A311-4544-9E0F-FF3C2903DE1A}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>F1:F1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5203,10 +5304,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>57</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -5220,30 +5321,30 @@
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
       <c r="D3" s="40"/>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="41">
         <v>84.1</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="44">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="47"/>
-      <c r="C5" s="49" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="48" t="s">
         <v>70</v>
       </c>
       <c r="D5" s="37" t="s">
@@ -5257,30 +5358,30 @@
       </c>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="40"/>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="41">
         <v>93.5</v>
       </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="44" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="44">
         <v>91.9</v>
       </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="37" t="s">
         <v>55</v>
       </c>
@@ -5292,24 +5393,24 @@
       </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
       <c r="D9" s="40"/>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <v>158.5</v>
       </c>
     </row>
@@ -5328,10 +5429,10 @@
       <c r="F12" s="36"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="45" t="s">
         <v>57</v>
       </c>
       <c r="D13" s="37" t="s">
@@ -5345,30 +5446,30 @@
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
       <c r="D14" s="40"/>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="41">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="44" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="44">
         <v>81.099999999999994</v>
       </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="47"/>
-      <c r="C16" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="48" t="s">
         <v>70</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -5382,30 +5483,30 @@
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
       <c r="D17" s="40"/>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="41">
         <v>91</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44" t="s">
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="44">
         <v>89.1</v>
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="37" t="s">
         <v>55</v>
       </c>
@@ -5417,24 +5518,24 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="44" t="s">
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="44">
         <v>90.3</v>
       </c>
     </row>
@@ -5453,8 +5554,6 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
     <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
@@ -5482,9 +5581,6 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F2:F21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{4933C17E-A4B9-8349-8CCF-C05CEDB1693A}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -5507,87 +5603,87 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="53">
+      <c r="F2" s="52">
         <v>86.8</v>
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="56">
         <v>86.9</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="54"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="59">
         <v>85.8</v>
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="54"/>
-      <c r="C5" s="50" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="56">
         <v>95.8</v>
       </c>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="56">
         <v>96.1</v>
       </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="59">
         <v>94.2</v>
       </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="62"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="61"/>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
@@ -5598,52 +5694,52 @@
       </c>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63" t="s">
+      <c r="D13" s="62"/>
+      <c r="E13" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="63">
         <v>181.6</v>
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="66"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="52" t="s">
+      <c r="B14" s="65"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="52">
         <v>91.5</v>
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="67"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="56">
         <v>91.8</v>
       </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="68"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59" t="s">
+      <c r="B16" s="67"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="59">
         <v>89.6</v>
       </c>
     </row>
@@ -5663,6 +5759,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F13:F16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{64AD8B08-10ED-554A-B62C-A7971C01EF30}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F14:F16">
     <cfRule type="dataBar" priority="2">
       <dataBar>
@@ -5673,20 +5783,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{DAB44C7F-2B31-1E4E-954E-3B8E9E2390E1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F16">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64AD8B08-10ED-554A-B62C-A7971C01EF30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5708,6 +5804,17 @@
           <xm:sqref>F2:F8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{64AD8B08-10ED-554A-B62C-A7971C01EF30}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F13:F16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DAB44C7F-2B31-1E4E-954E-3B8E9E2390E1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -5717,17 +5824,6 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>F14:F16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64AD8B08-10ED-554A-B62C-A7971C01EF30}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>F13:F16</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5741,154 +5837,154 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="53">
+      <c r="F2" s="52">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="56">
         <v>84.5</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="54"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="59">
         <v>82.9</v>
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="54"/>
-      <c r="C5" s="50" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="56">
         <v>90.1</v>
       </c>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="56">
         <v>92.5</v>
       </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="59">
         <v>91.2</v>
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="52">
         <v>79.099999999999994</v>
       </c>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="54"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56" t="s">
+      <c r="B11" s="53"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F11" s="56">
         <v>81.099999999999994</v>
       </c>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="54"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59" t="s">
+      <c r="B12" s="53"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="59">
         <v>79.599999999999994</v>
       </c>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="54"/>
-      <c r="C13" s="51" t="s">
+      <c r="B13" s="53"/>
+      <c r="C13" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="54"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="56">
         <v>89.7</v>
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="61"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="59">
         <v>89.6</v>
       </c>
     </row>
@@ -5957,180 +6053,201 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B3460A-5C2D-2D42-8B7F-136D9CA7CA67}">
-  <dimension ref="A2:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+    <row r="1" spans="1:6" ht="21" thickBot="1"/>
+    <row r="2" spans="1:6" ht="21" thickBot="1">
+      <c r="A2" s="69"/>
+      <c r="B2" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="70" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="F2" s="71"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="69" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="F3" s="71"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="69"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="43" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="F4" s="71"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="69"/>
+      <c r="B5" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
+      <c r="F5" s="71"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="69" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
+      <c r="F6" s="71"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="69"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="43" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="F7" s="71"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="69"/>
+      <c r="B8" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="38">
         <v>1965</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="38" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="F8" s="71"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="69"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="69" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
+      <c r="F9" s="71"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="69"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="43" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="F10" s="71"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="69"/>
+      <c r="B11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="38" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+      <c r="F11" s="71"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="69"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="43" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
+      <c r="F12" s="71"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="69"/>
+      <c r="B13" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="68" t="s">
         <v>26</v>
       </c>
+      <c r="F13" s="71"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="D6:D7" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/3_sekiguchi/関口実験.xlsx
+++ b/3_sekiguchi/関口実験.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/takumi/Documents/4e_zikken/3_sekiguchi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267CDFF3-03A7-2C4C-82DD-849ABB31B9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FEA3B6-15E4-C64E-89F5-0CB6771BD7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="6" xr2:uid="{89831BD7-977B-D94C-A7FA-04153F44CAF8}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{89831BD7-977B-D94C-A7FA-04153F44CAF8}"/>
   </bookViews>
   <sheets>
     <sheet name="実験2.1 無負荷試験" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
   <si>
     <t>W_i</t>
     <phoneticPr fontId="1"/>
@@ -476,6 +476,54 @@
     <rPh sb="0" eb="2">
       <t>シュベｔウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YMABASHI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S3P-240-10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0DJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スライド抵抗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R-858</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T6-1356</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R-865</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オシロスコープ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Agilent Technologies</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DSO 10 12A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CN50046662</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -521,12 +569,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="31">
@@ -917,7 +971,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1029,109 +1083,118 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2077,37 +2140,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -2151,56 +2184,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.40894224128227935"/>
-                  <c:y val="-8.1774004291758018E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'実験2.2 実負荷試験'!$H$3:$H$8</c:f>
@@ -2506,6 +2489,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>負荷電流</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
+                  <a:t> I_2 [A]</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="ja-JP"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2570,6 +2613,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>電圧</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t> [V]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2618,6 +2721,66 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>効率</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>n</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -3915,15 +4078,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>880418</xdr:colOff>
+      <xdr:colOff>880417</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>145879</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>689918</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>24369</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>550064</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>202229</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4900,29 +5063,42 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C12FBF-21A9-3F42-8CE5-32BFCB251E46}">
-  <dimension ref="B2:J27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="2" max="5" width="10.7109375" style="6"/>
+    <col min="2" max="3" width="10.7109375" style="6"/>
+    <col min="4" max="4" width="12" style="6" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="6" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="36"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" s="37" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="37"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="37"/>
+      <c r="B2" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="47">
         <v>43.4</v>
       </c>
+      <c r="G2" s="37"/>
       <c r="H2" s="6" t="s">
         <v>77</v>
       </c>
@@ -4933,16 +5109,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="6" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="37"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="49">
         <v>42.6</v>
       </c>
+      <c r="G3" s="37"/>
       <c r="I3" t="s">
         <v>79</v>
       </c>
@@ -4950,16 +5128,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="37"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="44">
+      <c r="F4" s="51">
         <v>42.7</v>
       </c>
+      <c r="G4" s="37"/>
       <c r="H4" s="6" t="s">
         <v>80</v>
       </c>
@@ -4970,18 +5150,20 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="37" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="37"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="47">
         <v>80</v>
       </c>
+      <c r="G5" s="37"/>
       <c r="I5" t="s">
         <v>79</v>
       </c>
@@ -4989,16 +5171,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="6" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="37"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="49">
         <v>80</v>
       </c>
+      <c r="G6" s="37"/>
       <c r="H6" t="s">
         <v>81</v>
       </c>
@@ -5006,234 +5190,308 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="40"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" s="37"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="51">
         <v>79.3</v>
       </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="40"/>
-      <c r="C8" s="48" t="s">
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="37"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="47">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="6" t="s">
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="37"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="49">
         <v>47.1</v>
       </c>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43" t="s">
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="37"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="51">
         <v>47.3</v>
       </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40" t="s">
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="37"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="49">
         <v>88.8</v>
       </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="6" t="s">
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="37"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="49">
         <v>88.6</v>
       </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43" t="s">
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="37"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="51">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="45" t="s">
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="37"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="37"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="37"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="37"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="37"/>
+      <c r="B16" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="47">
         <v>43.1</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="6" t="s">
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="37"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="49">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43" t="s">
+      <c r="G17" s="37"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="37"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="51">
         <v>44.9</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="37" t="s">
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="37"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="47">
         <v>84.1</v>
       </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="6" t="s">
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="37"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="49">
         <v>84.9</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="46"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43" t="s">
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="37"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="51">
         <v>83.2</v>
       </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="46"/>
-      <c r="C22" s="48" t="s">
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="37"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="47">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="6" t="s">
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="37"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="49">
         <v>49.5</v>
       </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="43" t="s">
+      <c r="G23" s="37"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="37"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="51">
         <v>49.1</v>
       </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="37" t="s">
+      <c r="G24" s="37"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="37"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="47">
         <v>92.5</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="6" t="s">
+      <c r="G25" s="37"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="37"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="49">
         <v>49.5</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="43" t="s">
+      <c r="G26" s="37"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="37"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="51">
         <v>47.9</v>
       </c>
+      <c r="G27" s="37"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="37"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="37"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5300,244 +5558,311 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DB7BD6-AFC2-F14A-9450-64BABAF67503}">
-  <dimension ref="B2:F21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:6">
-      <c r="B2" s="45" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="37"/>
+      <c r="B2" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="47">
         <v>84.1</v>
       </c>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="6" t="s">
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="37"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="49">
         <v>84.1</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43" t="s">
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="37"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="44">
+      <c r="F4" s="51">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="46"/>
-      <c r="C5" s="48" t="s">
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="37"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="47">
         <v>93.1</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="6" t="s">
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="37"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="49">
         <v>93.5</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43" t="s">
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="37"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="51">
         <v>91.9</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="37" t="s">
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="37"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="47">
         <v>161</v>
       </c>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="6" t="s">
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="37"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="49">
         <v>159</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43" t="s">
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="37"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="51">
         <v>158.5</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="36"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="36"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="45" t="s">
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="37"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="37"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="37"/>
+      <c r="B13" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="47">
         <v>82.9</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="6" t="s">
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="37"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="49">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="46"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43" t="s">
+      <c r="G14" s="37"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="37"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="51">
         <v>81.099999999999994</v>
       </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="46"/>
-      <c r="C16" s="48" t="s">
+      <c r="G15" s="37"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="37"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="47">
         <v>90.7</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="6" t="s">
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="37"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="49">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43" t="s">
+      <c r="G17" s="37"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="37"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="51">
         <v>89.1</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="37" t="s">
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="37"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="47">
         <v>159.1</v>
       </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="6" t="s">
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="37"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="49">
         <v>91</v>
       </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43" t="s">
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="37"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="51">
         <v>90.3</v>
       </c>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5599,149 +5924,212 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF5BBB3-EB12-BA49-A439-35ADC5355149}">
-  <dimension ref="B2:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:6">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="37"/>
+      <c r="B2" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="52">
+      <c r="F2" s="59">
         <v>86.8</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="37"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="63">
         <v>86.9</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="53"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="37"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="66">
         <v>85.8</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="53"/>
-      <c r="C5" s="49" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="37"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="63">
         <v>95.8</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="37"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="63">
         <v>96.1</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="37"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="66">
         <v>94.2</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="61"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="37"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="68"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="37"/>
+      <c r="B10" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C10" s="37"/>
+      <c r="D10" s="37" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="64" t="s">
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="37"/>
+      <c r="B13" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62" t="s">
+      <c r="D13" s="70"/>
+      <c r="E13" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="71">
         <v>181.6</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="65"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="51" t="s">
+    <row r="14" spans="1:6">
+      <c r="A14" s="37"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="59">
         <v>91.5</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="66"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="37"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="63">
         <v>91.8</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="67"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="37"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="66">
         <v>89.6</v>
       </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5833,160 +6221,220 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE500F1D-B182-CD44-9B12-94C95D65F9BC}">
-  <dimension ref="B2:F15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:6">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="37"/>
+      <c r="B2" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="52">
+      <c r="F2" s="59">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55" t="s">
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="37"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="63">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="53"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58" t="s">
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="37"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="66">
         <v>82.9</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="53"/>
-      <c r="C5" s="49" t="s">
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="37"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="63">
         <v>90.1</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55" t="s">
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="37"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="63">
         <v>92.5</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58" t="s">
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="37"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="66">
         <v>91.2</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="49" t="s">
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="37"/>
+      <c r="B10" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="59">
         <v>79.099999999999994</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="53"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55" t="s">
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="63">
         <v>81.099999999999994</v>
       </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="53"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58" t="s">
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="37"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="66">
         <v>79.599999999999994</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="53"/>
-      <c r="C13" s="50" t="s">
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="37"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="63">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55" t="s">
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="37"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="63">
         <v>89.7</v>
       </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="60"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58" t="s">
+      <c r="G14" s="37"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="37"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="66">
         <v>89.6</v>
       </c>
+      <c r="G15" s="37"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -6053,194 +6501,284 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B3460A-5C2D-2D42-8B7F-136D9CA7CA67}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" thickBot="1"/>
+    <row r="1" spans="1:6" ht="21" thickBot="1">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
     <row r="2" spans="1:6" ht="21" thickBot="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70" t="s">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="71"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="69"/>
-      <c r="B3" s="69" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="71"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="69"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43" t="s">
+      <c r="A4" s="38"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="71"/>
+      <c r="F4" s="40"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="69"/>
-      <c r="B5" s="38" t="s">
+      <c r="A5" s="38"/>
+      <c r="B5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="71"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69" t="s">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="71"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="69"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="71"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="69"/>
-      <c r="B8" s="38" t="s">
+      <c r="A8" s="38"/>
+      <c r="B8" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="42">
         <v>1965</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="71"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="69"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="71"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="69"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="71"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="69"/>
-      <c r="B11" s="38" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="71"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="69"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="71"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="69"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="40"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="38"/>
+      <c r="B14" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="40"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="40"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="40"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="38"/>
+      <c r="B17" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="40"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="38"/>
+      <c r="B18" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C18" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="D18" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E18" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="71"/>
+      <c r="F18" s="40"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
